--- a/examples/Methylene Blue Diffusion Parameter Fitting/drug-eluting hydrogel implants.jl/drug_eluting_hydrogel_implant_normal_natural_diffusion_results.xlsx
+++ b/examples/Methylene Blue Diffusion Parameter Fitting/drug-eluting hydrogel implants.jl/drug_eluting_hydrogel_implant_normal_natural_diffusion_results.xlsx
@@ -406,7 +406,7 @@
         <v>18.0</v>
       </c>
       <c r="B3">
-        <v>1.2305751795159042e-90</v>
+        <v>4.419595450654984e-25</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -414,7 +414,7 @@
         <v>36.0</v>
       </c>
       <c r="B4">
-        <v>1.0424867300220628e-84</v>
+        <v>7.269774917677281e-20</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -422,7 +422,7 @@
         <v>54.0</v>
       </c>
       <c r="B5">
-        <v>1.735475195826566e-82</v>
+        <v>2.683986432947902e-17</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -430,7 +430,7 @@
         <v>72.0</v>
       </c>
       <c r="B6">
-        <v>7.464885655263961e-81</v>
+        <v>1.1987544822966533e-15</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -438,7 +438,7 @@
         <v>90.0</v>
       </c>
       <c r="B7">
-        <v>1.2832310912137142e-79</v>
+        <v>2.0638797867555662e-14</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -446,7 +446,7 @@
         <v>108.0</v>
       </c>
       <c r="B8">
-        <v>1.3036314534791062e-78</v>
+        <v>1.9772679943108187e-13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -454,7 +454,7 @@
         <v>126.0</v>
       </c>
       <c r="B9">
-        <v>9.914196561173723e-78</v>
+        <v>1.3925195206831792e-12</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -462,7 +462,7 @@
         <v>144.0</v>
       </c>
       <c r="B10">
-        <v>5.264802456784925e-77</v>
+        <v>6.967892608009686e-12</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -470,7 +470,7 @@
         <v>162.0</v>
       </c>
       <c r="B11">
-        <v>2.4580090900400813e-76</v>
+        <v>2.6212195249857594e-11</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -478,7 +478,7 @@
         <v>180.0</v>
       </c>
       <c r="B12">
-        <v>9.36463699479984e-76</v>
+        <v>9.040259786729121e-11</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -486,7 +486,7 @@
         <v>198.0</v>
       </c>
       <c r="B13">
-        <v>3.1144498207270326e-75</v>
+        <v>2.494536462562238e-10</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -494,7 +494,7 @@
         <v>216.0</v>
       </c>
       <c r="B14">
-        <v>9.687421973743596e-75</v>
+        <v>6.317927009357607e-10</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -502,7 +502,7 @@
         <v>234.0</v>
       </c>
       <c r="B15">
-        <v>2.6621327405949237e-74</v>
+        <v>1.4542408681356607e-9</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -510,7 +510,7 @@
         <v>252.0</v>
       </c>
       <c r="B16">
-        <v>6.722662027648483e-74</v>
+        <v>3.1452437009470446e-9</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -518,7 +518,7 @@
         <v>270.0</v>
       </c>
       <c r="B17">
-        <v>1.644491609718012e-73</v>
+        <v>6.055249670907293e-9</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -526,7 +526,7 @@
         <v>288.0</v>
       </c>
       <c r="B18">
-        <v>3.759745470621681e-73</v>
+        <v>1.1262157183159482e-8</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -534,7 +534,7 @@
         <v>306.0</v>
       </c>
       <c r="B19">
-        <v>8.061392683238283e-73</v>
+        <v>1.9141763729265792e-8</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -542,7 +542,7 @@
         <v>324.0</v>
       </c>
       <c r="B20">
-        <v>1.666916160523692e-72</v>
+        <v>3.1705558695230857e-8</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -550,7 +550,7 @@
         <v>342.0</v>
       </c>
       <c r="B21">
-        <v>3.3245446044083667e-72</v>
+        <v>4.9740300747243146e-8</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -558,7 +558,7 @@
         <v>360.0</v>
       </c>
       <c r="B22">
-        <v>6.363359664776057e-72</v>
+        <v>7.617801375470736e-8</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -566,7 +566,7 @@
         <v>378.0</v>
       </c>
       <c r="B23">
-        <v>1.1790137190441593e-71</v>
+        <v>1.1285982778563056e-7</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -574,7 +574,7 @@
         <v>396.0</v>
       </c>
       <c r="B24">
-        <v>2.1246408548722432e-71</v>
+        <v>1.6101544184047644e-7</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -582,7 +582,7 @@
         <v>414.0</v>
       </c>
       <c r="B25">
-        <v>3.723036938085809e-71</v>
+        <v>2.2535563223235438e-7</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -590,7 +590,7 @@
         <v>432.0</v>
       </c>
       <c r="B26">
-        <v>6.36792596749703e-71</v>
+        <v>3.0780476102577495e-7</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -598,7 +598,7 @@
         <v>450.0</v>
       </c>
       <c r="B27">
-        <v>1.065246625601536e-70</v>
+        <v>4.1021612000648794e-7</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -606,7 +606,7 @@
         <v>468.0</v>
       </c>
       <c r="B28">
-        <v>1.7451448083937157e-70</v>
+        <v>5.369578270133946e-7</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -614,7 +614,7 @@
         <v>486.0</v>
       </c>
       <c r="B29">
-        <v>2.8058427998895052e-70</v>
+        <v>6.916345529627738e-7</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -622,7 +622,7 @@
         <v>504.0</v>
       </c>
       <c r="B30">
-        <v>4.431831522939439e-70</v>
+        <v>8.776381060193313e-7</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -630,7 +630,7 @@
         <v>522.0</v>
       </c>
       <c r="B31">
-        <v>6.887274240603905e-70</v>
+        <v>1.0979041522003997e-6</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -638,7 +638,7 @@
         <v>540.0</v>
       </c>
       <c r="B32">
-        <v>1.0540976742264801e-69</v>
+        <v>1.3543920945603718e-6</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -646,7 +646,7 @@
         <v>558.0</v>
       </c>
       <c r="B33">
-        <v>1.5905435008603978e-69</v>
+        <v>1.6512048683728654e-6</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -654,7 +654,7 @@
         <v>576.0</v>
       </c>
       <c r="B34">
-        <v>2.3683713749022835e-69</v>
+        <v>1.9926611285511813e-6</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -662,7 +662,7 @@
         <v>594.0</v>
       </c>
       <c r="B35">
-        <v>3.482701235892493e-69</v>
+        <v>2.38162148693612e-6</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -670,7 +670,7 @@
         <v>612.0</v>
       </c>
       <c r="B36">
-        <v>5.062009332496808e-69</v>
+        <v>2.81712817124844e-6</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -678,7 +678,7 @@
         <v>630.0</v>
       </c>
       <c r="B37">
-        <v>7.276388063867569e-69</v>
+        <v>3.302520695403808e-6</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -686,7 +686,7 @@
         <v>648.0</v>
       </c>
       <c r="B38">
-        <v>1.0351661159571438e-68</v>
+        <v>3.841549125624628e-6</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -694,7 +694,7 @@
         <v>666.0</v>
       </c>
       <c r="B39">
-        <v>1.4582429557018254e-68</v>
+        <v>4.436500648261752e-6</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -702,7 +702,7 @@
         <v>684.0</v>
       </c>
       <c r="B40">
-        <v>2.0351964491086182e-68</v>
+        <v>5.085407466054063e-6</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -710,7 +710,7 @@
         <v>702.0</v>
       </c>
       <c r="B41">
-        <v>2.8156008331313206e-68</v>
+        <v>5.78888071082648e-6</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -718,7 +718,7 @@
         <v>720.0</v>
       </c>
       <c r="B42">
-        <v>3.8626927042367426e-68</v>
+        <v>6.547771392595677e-6</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -726,7 +726,7 @@
         <v>738.0</v>
       </c>
       <c r="B43">
-        <v>5.2574081984644554e-68</v>
+        <v>7.362930521378334e-6</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -734,7 +734,7 @@
         <v>756.0</v>
       </c>
       <c r="B44">
-        <v>7.101782543101959e-68</v>
+        <v>8.234524303874684e-6</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -742,7 +742,7 @@
         <v>774.0</v>
       </c>
       <c r="B45">
-        <v>9.524290966951979e-68</v>
+        <v>9.16123662304493e-6</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -750,7 +750,7 @@
         <v>792.0</v>
       </c>
       <c r="B46">
-        <v>1.2686021673415995e-67</v>
+        <v>1.0141764338137883e-5</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -758,7 +758,7 @@
         <v>810.0</v>
       </c>
       <c r="B47">
-        <v>1.6786662236625396e-67</v>
+        <v>1.1174804701711856e-5</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -766,7 +766,7 @@
         <v>828.0</v>
       </c>
       <c r="B48">
-        <v>2.207440369632182e-67</v>
+        <v>1.2259054966325153e-5</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -774,7 +774,7 @@
         <v>846.0</v>
       </c>
       <c r="B49">
-        <v>2.885430464512987e-67</v>
+        <v>1.339361476514944e-5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -782,7 +782,7 @@
         <v>864.0</v>
       </c>
       <c r="B50">
-        <v>3.750059694733653e-67</v>
+        <v>1.4578862615732686e-5</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -790,7 +790,7 @@
         <v>882.0</v>
       </c>
       <c r="B51">
-        <v>4.8471095547027627e-67</v>
+        <v>1.5812392837071632e-5</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -798,7 +798,7 @@
         <v>900.0</v>
       </c>
       <c r="B52">
-        <v>6.23207994301852e-67</v>
+        <v>1.709138809038416e-5</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -806,7 +806,7 @@
         <v>918.0</v>
       </c>
       <c r="B53">
-        <v>7.97236769385265e-67</v>
+        <v>1.8413031036888145e-5</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -814,7 +814,7 @@
         <v>936.0</v>
       </c>
       <c r="B54">
-        <v>1.0149117082642493e-66</v>
+        <v>1.9774504337801462e-5</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -822,7 +822,7 @@
         <v>954.0</v>
       </c>
       <c r="B55">
-        <v>1.2859864782605696e-66</v>
+        <v>2.1172841489352483e-5</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -830,7 +830,7 @@
         <v>972.0</v>
       </c>
       <c r="B56">
-        <v>1.6221545232356361e-66</v>
+        <v>2.2601866344755076e-5</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -838,7 +838,7 @@
         <v>990.0</v>
       </c>
       <c r="B57">
-        <v>2.0373378816095267e-66</v>
+        <v>2.4061096439739162e-5</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -846,7 +846,7 @@
         <v>1008.0</v>
       </c>
       <c r="B58">
-        <v>2.5481315396190074e-66</v>
+        <v>2.5552734067533974e-5</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -854,7 +854,7 @@
         <v>1026.0</v>
       </c>
       <c r="B59">
-        <v>3.174174866400588e-66</v>
+        <v>2.7078981521368756e-5</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -862,7 +862,7 @@
         <v>1044.0</v>
       </c>
       <c r="B60">
-        <v>3.938686728052365e-66</v>
+        <v>2.864091782387185e-5</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -870,7 +870,7 @@
         <v>1062.0</v>
       </c>
       <c r="B61">
-        <v>4.8690454742593e-66</v>
+        <v>3.0223032684260143e-5</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -878,7 +878,7 @@
         <v>1080.0</v>
       </c>
       <c r="B62">
-        <v>5.997362206660329e-66</v>
+        <v>3.182325428829194e-5</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -886,7 +886,7 @@
         <v>1098.0</v>
       </c>
       <c r="B63">
-        <v>7.361330389295378e-66</v>
+        <v>3.3446182821579325e-5</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -894,7 +894,7 @@
         <v>1116.0</v>
       </c>
       <c r="B64">
-        <v>9.004923705745944e-66</v>
+        <v>3.509641846973441e-5</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -902,7 +902,7 @@
         <v>1134.0</v>
       </c>
       <c r="B65">
-        <v>1.0979415456919292e-65</v>
+        <v>3.67761806522564e-5</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -910,7 +910,7 @@
         <v>1152.0</v>
       </c>
       <c r="B66">
-        <v>1.3344434302899361e-65</v>
+        <v>3.8466006710249016e-5</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -918,7 +918,7 @@
         <v>1170.0</v>
       </c>
       <c r="B67">
-        <v>1.6169037870986537e-65</v>
+        <v>4.0164714652372684e-5</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -926,7 +926,7 @@
         <v>1188.0</v>
       </c>
       <c r="B68">
-        <v>1.9533247810523266e-65</v>
+        <v>4.1877495474300415e-5</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -934,7 +934,7 @@
         <v>1206.0</v>
       </c>
       <c r="B69">
-        <v>2.3529298166890228e-65</v>
+        <v>4.360954017170517e-5</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -942,7 +942,7 @@
         <v>1224.0</v>
       </c>
       <c r="B70">
-        <v>2.826347657029576e-65</v>
+        <v>4.536244881989523e-5</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -950,7 +950,7 @@
         <v>1242.0</v>
       </c>
       <c r="B71">
-        <v>3.3857953686466106e-65</v>
+        <v>4.7116578101057274e-5</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -958,7 +958,7 @@
         <v>1260.0</v>
       </c>
       <c r="B72">
-        <v>4.0452699838200724e-65</v>
+        <v>4.887221638002434e-5</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -966,7 +966,7 @@
         <v>1278.0</v>
       </c>
       <c r="B73">
-        <v>4.820812720433344e-65</v>
+        <v>5.063435713688281e-5</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -974,7 +974,7 @@
         <v>1296.0</v>
       </c>
       <c r="B74">
-        <v>5.73072320395437e-65</v>
+        <v>5.2407993851719036e-5</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -982,7 +982,7 @@
         <v>1314.0</v>
       </c>
       <c r="B75">
-        <v>6.795877521589928e-65</v>
+        <v>5.4193556475218615e-5</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -990,7 +990,7 @@
         <v>1332.0</v>
       </c>
       <c r="B76">
-        <v>8.040031628818566e-65</v>
+        <v>5.5973419558542545e-5</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -998,7 +998,7 @@
         <v>1350.0</v>
       </c>
       <c r="B77">
-        <v>9.490150443236008e-65</v>
+        <v>5.774900627605449e-5</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1006,7 +1006,7 @@
         <v>1368.0</v>
       </c>
       <c r="B78">
-        <v>1.1176843788768114e-64</v>
+        <v>5.952472624106041e-5</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1014,7 +1014,7 @@
         <v>1386.0</v>
       </c>
       <c r="B79">
-        <v>1.313472085986138e-64</v>
+        <v>6.130498906686629e-5</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1022,7 +1022,7 @@
         <v>1404.0</v>
       </c>
       <c r="B80">
-        <v>1.5402919548461724e-64</v>
+        <v>6.309091991544319e-5</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1030,7 +1030,7 @@
         <v>1422.0</v>
       </c>
       <c r="B81">
-        <v>1.8025590337637485e-64</v>
+        <v>6.48728538695484e-5</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1038,7 +1038,7 @@
         <v>1440.0</v>
       </c>
       <c r="B82">
-        <v>2.105244278853154e-64</v>
+        <v>6.664916151427311e-5</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1046,7 +1046,7 @@
         <v>1458.0</v>
       </c>
       <c r="B83">
-        <v>2.4539438826669007e-64</v>
+        <v>6.841915983268609e-5</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1054,7 +1054,7 @@
         <v>1476.0</v>
       </c>
       <c r="B84">
-        <v>2.8549361321949414e-64</v>
+        <v>7.018216580785607e-5</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1062,7 +1062,7 @@
         <v>1494.0</v>
       </c>
       <c r="B85">
-        <v>3.315266601569361e-64</v>
+        <v>7.193749642285176e-5</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1070,7 +1070,7 @@
         <v>1512.0</v>
       </c>
       <c r="B86">
-        <v>3.8428228755731e-64</v>
+        <v>7.368446866074195e-5</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1078,7 +1078,7 @@
         <v>1530.0</v>
       </c>
       <c r="B87">
-        <v>4.4464225058027015e-64</v>
+        <v>7.542239950459534e-5</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1086,7 +1086,7 @@
         <v>1548.0</v>
       </c>
       <c r="B88">
-        <v>5.135919841810796e-64</v>
+        <v>7.715095248325681e-5</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1094,7 +1094,7 @@
         <v>1566.0</v>
       </c>
       <c r="B89">
-        <v>5.922294861672839e-64</v>
+        <v>7.887186016191126e-5</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1102,7 +1102,7 @@
         <v>1584.0</v>
       </c>
       <c r="B90">
-        <v>6.817786094870979e-64</v>
+        <v>8.058437845197761e-5</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1110,7 +1110,7 @@
         <v>1602.0</v>
       </c>
       <c r="B91">
-        <v>7.836003066515977e-64</v>
+        <v>8.228718167338458e-5</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1118,7 +1118,7 @@
         <v>1620.0</v>
       </c>
       <c r="B92">
-        <v>8.992063738511102e-64</v>
+        <v>8.397894414606085e-5</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1126,7 +1126,7 @@
         <v>1638.0</v>
       </c>
       <c r="B93">
-        <v>1.0302754746285365e-63</v>
+        <v>8.565834018993517e-5</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1134,7 +1134,7 @@
         <v>1656.0</v>
       </c>
       <c r="B94">
-        <v>1.1786667026370904e-63</v>
+        <v>8.73240441249362e-5</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1142,7 +1142,7 @@
         <v>1674.0</v>
       </c>
       <c r="B95">
-        <v>1.3464397399837872e-63</v>
+        <v>8.897473027099269e-5</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1150,7 +1150,7 @@
         <v>1692.0</v>
       </c>
       <c r="B96">
-        <v>1.5358714261208533e-63</v>
+        <v>9.060907294803333e-5</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1158,7 +1158,7 @@
         <v>1710.0</v>
       </c>
       <c r="B97">
-        <v>1.749476647560007e-63</v>
+        <v>9.222574647598685e-5</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1166,7 +1166,7 @@
         <v>1728.0</v>
       </c>
       <c r="B98">
-        <v>1.9900318240791843e-63</v>
+        <v>9.382342517478194e-5</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1174,7 +1174,7 @@
         <v>1746.0</v>
       </c>
       <c r="B99">
-        <v>2.2605951941470935e-63</v>
+        <v>9.540637997608068e-5</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1182,7 +1182,7 @@
         <v>1764.0</v>
       </c>
       <c r="B100">
-        <v>2.5645366114693255e-63</v>
+        <v>9.697890855737051e-5</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1190,7 +1190,7 @@
         <v>1782.0</v>
       </c>
       <c r="B101">
-        <v>2.9055615100884127e-63</v>
+        <v>9.853966433776067e-5</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1198,7 +1198,7 @@
         <v>1800.0</v>
       </c>
       <c r="B102">
-        <v>3.287741907935624e-63</v>
+        <v>0.00010008730071789707</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1206,7 +1206,7 @@
         <v>1818.0</v>
       </c>
       <c r="B103">
-        <v>3.7155500946744717e-63</v>
+        <v>0.00010162047109842571</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1214,7 +1214,7 @@
         <v>1836.0</v>
       </c>
       <c r="B104">
-        <v>4.1938884408223e-63</v>
+        <v>0.00010313782887999251</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1222,7 +1222,7 @@
         <v>1854.0</v>
       </c>
       <c r="B105">
-        <v>4.728132439152395e-63</v>
+        <v>0.00010463802746324345</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1230,7 +1230,7 @@
         <v>1872.0</v>
       </c>
       <c r="B106">
-        <v>5.324164709934992e-63</v>
+        <v>0.00010611972024882445</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1238,7 +1238,7 @@
         <v>1890.0</v>
       </c>
       <c r="B107">
-        <v>5.988420253639275e-63</v>
+        <v>0.0001075815606373815</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1246,7 +1246,7 @@
         <v>1908.0</v>
       </c>
       <c r="B108">
-        <v>6.727933621323598e-63</v>
+        <v>0.00010902220202956052</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1254,7 +1254,7 @@
         <v>1926.0</v>
       </c>
       <c r="B109">
-        <v>7.550382136793984e-63</v>
+        <v>0.00011044185986412978</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1262,7 +1262,7 @@
         <v>1944.0</v>
       </c>
       <c r="B110">
-        <v>8.4641467462096e-63</v>
+        <v>0.00011184716802193605</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1270,7 +1270,7 @@
         <v>1962.0</v>
       </c>
       <c r="B111">
-        <v>9.478359499995524e-63</v>
+        <v>0.00011323866487473765</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1278,7 +1278,7 @@
         <v>1980.0</v>
       </c>
       <c r="B112">
-        <v>1.06029685325055e-62</v>
+        <v>0.0001146159020490777</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1286,7 +1286,7 @@
         <v>1998.0</v>
       </c>
       <c r="B113">
-        <v>1.1848802730781791e-62</v>
+        <v>0.00011597843117149943</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1294,7 +1294,7 @@
         <v>2016.0</v>
       </c>
       <c r="B114">
-        <v>1.322763359943368e-62</v>
+        <v>0.00011732580386854598</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1302,7 +1302,7 @@
         <v>2034.0</v>
       </c>
       <c r="B115">
-        <v>1.4752259605500015e-62</v>
+        <v>0.00011865757176676052</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1310,7 +1310,7 @@
         <v>2052.0</v>
       </c>
       <c r="B116">
-        <v>1.6436571601056231e-62</v>
+        <v>0.00011997328649268628</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1318,7 +1318,7 @@
         <v>2070.0</v>
       </c>
       <c r="B117">
-        <v>1.8295644621663955e-62</v>
+        <v>0.00012127249967286636</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1326,7 +1326,7 @@
         <v>2088.0</v>
       </c>
       <c r="B118">
-        <v>2.0345824957757837e-62</v>
+        <v>0.00012255476293384398</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1334,7 +1334,7 @@
         <v>2106.0</v>
       </c>
       <c r="B119">
-        <v>2.2604817560274957e-62</v>
+        <v>0.00012381962790216234</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1342,7 +1342,7 @@
         <v>2124.0</v>
       </c>
       <c r="B120">
-        <v>2.5091800872860285e-62</v>
+        <v>0.00012506664620436458</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1350,7 +1350,7 @@
         <v>2142.0</v>
       </c>
       <c r="B121">
-        <v>2.7827515976361786e-62</v>
+        <v>0.00012629543589668123</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1358,7 +1358,7 @@
         <v>2160.0</v>
       </c>
       <c r="B122">
-        <v>3.0834394205795587e-62</v>
+        <v>0.00012750933503168232</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1366,7 +1366,7 @@
         <v>2178.0</v>
       </c>
       <c r="B123">
-        <v>3.413667261785389e-62</v>
+        <v>0.00012871025985895776</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1374,7 +1374,7 @@
         <v>2196.0</v>
       </c>
       <c r="B124">
-        <v>3.7760515858189945e-62</v>
+        <v>0.00012989800132981943</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1382,7 +1382,7 @@
         <v>2214.0</v>
       </c>
       <c r="B125">
-        <v>4.173416999480694e-62</v>
+        <v>0.00013107235039557923</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -1390,7 +1390,7 @@
         <v>2232.0</v>
       </c>
       <c r="B126">
-        <v>4.608808283907262e-62</v>
+        <v>0.00013223309800754912</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -1398,7 +1398,7 @@
         <v>2250.0</v>
       </c>
       <c r="B127">
-        <v>5.085507858340323e-62</v>
+        <v>0.0001333800351170409</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -1406,7 +1406,7 @@
         <v>2268.0</v>
       </c>
       <c r="B128">
-        <v>5.607050903566666e-62</v>
+        <v>0.00013451295267536653</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -1414,7 +1414,7 @@
         <v>2286.0</v>
       </c>
       <c r="B129">
-        <v>6.177242123762037e-62</v>
+        <v>0.0001356316416338379</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -1422,7 +1422,7 @@
         <v>2304.0</v>
       </c>
       <c r="B130">
-        <v>6.800176061789172e-62</v>
+        <v>0.00013673589294376683</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -1430,7 +1430,7 @@
         <v>2322.0</v>
       </c>
       <c r="B131">
-        <v>7.480253204005164e-62</v>
+        <v>0.00013782549755646532</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -1438,7 +1438,7 @@
         <v>2340.0</v>
       </c>
       <c r="B132">
-        <v>8.222203514757895e-62</v>
+        <v>0.0001389002464232452</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -1446,7 +1446,7 @@
         <v>2358.0</v>
       </c>
       <c r="B133">
-        <v>9.031106053014716e-62</v>
+        <v>0.00013995993049541837</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -1454,7 +1454,7 @@
         <v>2376.0</v>
       </c>
       <c r="B134">
-        <v>9.912411703906062e-62</v>
+        <v>0.00014100434072429673</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -1462,7 +1462,7 @@
         <v>2394.0</v>
       </c>
       <c r="B135">
-        <v>1.0871969678063166e-61</v>
+        <v>0.00014203326806119218</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1470,7 +1470,7 @@
         <v>2412.0</v>
       </c>
       <c r="B136">
-        <v>1.191604890140118e-61</v>
+        <v>0.0001430477898012832</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -1478,7 +1478,7 @@
         <v>2430.0</v>
       </c>
       <c r="B137">
-        <v>1.3051369263598534e-61</v>
+        <v>0.00014405164378812724</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -1486,7 +1486,7 @@
         <v>2448.0</v>
       </c>
       <c r="B138">
-        <v>1.4285126882197623e-61</v>
+        <v>0.00014504487673117417</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -1494,7 +1494,7 @@
         <v>2466.0</v>
       </c>
       <c r="B139">
-        <v>1.5625024482644467e-61</v>
+        <v>0.00014602725670184686</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -1502,7 +1502,7 @@
         <v>2484.0</v>
       </c>
       <c r="B140">
-        <v>1.7079305609950135e-61</v>
+        <v>0.00014699855177156842</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -1510,7 +1510,7 @@
         <v>2502.0</v>
       </c>
       <c r="B141">
-        <v>1.8656782824384157e-61</v>
+        <v>0.0001479585300117617</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -1518,7 +1518,7 @@
         <v>2520.0</v>
       </c>
       <c r="B142">
-        <v>2.0366878628059137e-61</v>
+        <v>0.0001489069594938497</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -1526,7 +1526,7 @@
         <v>2538.0</v>
       </c>
       <c r="B143">
-        <v>2.2219657735298526e-61</v>
+        <v>0.00014984360828925532</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -1534,7 +1534,7 @@
         <v>2556.0</v>
       </c>
       <c r="B144">
-        <v>2.4225867291844656e-61</v>
+        <v>0.00015076824446940164</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -1542,7 +1542,7 @@
         <v>2574.0</v>
       </c>
       <c r="B145">
-        <v>2.639698045692211e-61</v>
+        <v>0.0001516806361057115</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -1550,7 +1550,7 @@
         <v>2592.0</v>
       </c>
       <c r="B146">
-        <v>2.8745233399169242e-61</v>
+        <v>0.00015258055126960793</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -1558,7 +1558,7 @@
         <v>2610.0</v>
       </c>
       <c r="B147">
-        <v>3.128367819792927e-61</v>
+        <v>0.00015346775803251386</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -1566,7 +1566,7 @@
         <v>2628.0</v>
       </c>
       <c r="B148">
-        <v>3.402622372606557e-61</v>
+        <v>0.00015434202446585227</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -1574,7 +1574,7 @@
         <v>2646.0</v>
       </c>
       <c r="B149">
-        <v>3.698768851417455e-61</v>
+        <v>0.00015520311864104612</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -1582,7 +1582,7 @@
         <v>2664.0</v>
       </c>
       <c r="B150">
-        <v>4.0183855476937195e-61</v>
+        <v>0.0001560509221794825</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -1590,7 +1590,7 @@
         <v>2682.0</v>
       </c>
       <c r="B151">
-        <v>4.3631520286787274e-61</v>
+        <v>0.000156888487675295</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -1598,7 +1598,7 @@
         <v>2700.0</v>
       </c>
       <c r="B152">
-        <v>4.734855889101274e-61</v>
+        <v>0.00015771715276591557</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -1606,7 +1606,7 @@
         <v>2718.0</v>
       </c>
       <c r="B153">
-        <v>5.135397898098479e-61</v>
+        <v>0.00015853676210789215</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -1614,7 +1614,7 @@
         <v>2736.0</v>
       </c>
       <c r="B154">
-        <v>5.566798889909046e-61</v>
+        <v>0.00015934716035777277</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -1622,7 +1622,7 @@
         <v>2754.0</v>
       </c>
       <c r="B155">
-        <v>6.031206552214002e-61</v>
+        <v>0.0001601481921721054</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -1630,7 +1630,7 @@
         <v>2772.0</v>
       </c>
       <c r="B156">
-        <v>6.530901722355697e-61</v>
+        <v>0.00016093970220743808</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -1638,7 +1638,7 @@
         <v>2790.0</v>
       </c>
       <c r="B157">
-        <v>7.068306902916608e-61</v>
+        <v>0.00016172153512031886</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -1646,7 +1646,7 @@
         <v>2808.0</v>
       </c>
       <c r="B158">
-        <v>7.645992710912811e-61</v>
+        <v>0.00016249353556729572</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -1654,7 +1654,7 @@
         <v>2826.0</v>
       </c>
       <c r="B159">
-        <v>8.266686777230874e-61</v>
+        <v>0.0001632555482049166</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -1662,7 +1662,7 @@
         <v>2844.0</v>
       </c>
       <c r="B160">
-        <v>8.933282081748559e-61</v>
+        <v>0.00016400741768972965</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -1670,7 +1670,7 @@
         <v>2862.0</v>
       </c>
       <c r="B161">
-        <v>9.648845101461607e-61</v>
+        <v>0.00016474898867828279</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -1678,7 +1678,7 @@
         <v>2880.0</v>
       </c>
       <c r="B162">
-        <v>1.0416626434409401e-60</v>
+        <v>0.00016548010582712402</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -1686,7 +1686,7 @@
         <v>2898.0</v>
       </c>
       <c r="B163">
-        <v>1.124006885209663e-60</v>
+        <v>0.00016620061379280142</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -1694,7 +1694,7 @@
         <v>2916.0</v>
       </c>
       <c r="B164">
-        <v>1.212281868123163e-60</v>
+        <v>0.00016691035723186292</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -1702,7 +1702,7 @@
         <v>2934.0</v>
       </c>
       <c r="B165">
-        <v>1.306873595557416e-60</v>
+        <v>0.00016761014332953824</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -1710,7 +1710,7 @@
         <v>2952.0</v>
       </c>
       <c r="B166">
-        <v>1.4081904887777382e-60</v>
+        <v>0.0001683022141631246</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -1718,7 +1718,7 @@
         <v>2970.0</v>
       </c>
       <c r="B167">
-        <v>1.5166646994610749e-60</v>
+        <v>0.00016898659198847475</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -1726,7 +1726,7 @@
         <v>2988.0</v>
       </c>
       <c r="B168">
-        <v>1.6327531123280147e-60</v>
+        <v>0.0001696631915868161</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -1734,7 +1734,7 @@
         <v>3006.0</v>
       </c>
       <c r="B169">
-        <v>1.7569387861092178e-60</v>
+        <v>0.00017033192773937604</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -1742,7 +1742,7 @@
         <v>3024.0</v>
       </c>
       <c r="B170">
-        <v>1.8897321826246186e-60</v>
+        <v>0.00017099271522738195</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -1750,7 +1750,7 @@
         <v>3042.0</v>
       </c>
       <c r="B171">
-        <v>2.0316725017172165e-60</v>
+        <v>0.00017164546883206123</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -1758,7 +1758,7 @@
         <v>3060.0</v>
       </c>
       <c r="B172">
-        <v>2.18332928906753e-60</v>
+        <v>0.0001722901033346413</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -1766,7 +1766,7 @@
         <v>3078.0</v>
       </c>
       <c r="B173">
-        <v>2.3453036815499533e-60</v>
+        <v>0.0001729265335163495</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -1774,7 +1774,7 @@
         <v>3096.0</v>
       </c>
       <c r="B174">
-        <v>2.5182302129017397e-60</v>
+        <v>0.0001735546741584133</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -1782,7 +1782,7 @@
         <v>3114.0</v>
       </c>
       <c r="B175">
-        <v>2.7027782960557546e-60</v>
+        <v>0.00017417444004206006</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -1790,7 +1790,7 @@
         <v>3132.0</v>
       </c>
       <c r="B176">
-        <v>2.899653909140224e-60</v>
+        <v>0.00017478574594851715</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -1798,7 +1798,7 @@
         <v>3150.0</v>
       </c>
       <c r="B177">
-        <v>3.1096015512616705e-60</v>
+        <v>0.000175388506659012</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -1806,7 +1806,7 @@
         <v>3168.0</v>
       </c>
       <c r="B178">
-        <v>3.3334057854192204e-60</v>
+        <v>0.000175982636954772</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -1814,7 +1814,7 @@
         <v>3186.0</v>
       </c>
       <c r="B179">
-        <v>3.5718934784196083e-60</v>
+        <v>0.0001765681449266395</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -1822,7 +1822,7 @@
         <v>3204.0</v>
       </c>
       <c r="B180">
-        <v>3.825935584113571e-60</v>
+        <v>0.00017714660229952735</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -1830,7 +1830,7 @@
         <v>3222.0</v>
       </c>
       <c r="B181">
-        <v>4.0964492535594044e-60</v>
+        <v>0.00017771855900344994</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -1838,7 +1838,7 @@
         <v>3240.0</v>
       </c>
       <c r="B182">
-        <v>4.384400198577573e-60</v>
+        <v>0.0001782839633827739</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -1846,7 +1846,7 @@
         <v>3258.0</v>
       </c>
       <c r="B183">
-        <v>4.6908045990250897e-60</v>
+        <v>0.0001788427637818657</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -1854,7 +1854,7 @@
         <v>3276.0</v>
       </c>
       <c r="B184">
-        <v>5.016731855447385e-60</v>
+        <v>0.0001793949085450919</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -1862,7 +1862,7 @@
         <v>3294.0</v>
       </c>
       <c r="B185">
-        <v>5.363306724009696e-60</v>
+        <v>0.00017994034601681903</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -1870,7 +1870,7 @@
         <v>3312.0</v>
       </c>
       <c r="B186">
-        <v>5.731711948736679e-60</v>
+        <v>0.00018047902454141354</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -1878,7 +1878,7 @@
         <v>3330.0</v>
       </c>
       <c r="B187">
-        <v>6.123191086306369e-60</v>
+        <v>0.000181010892463242</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -1886,7 +1886,7 @@
         <v>3348.0</v>
       </c>
       <c r="B188">
-        <v>6.539050865624392e-60</v>
+        <v>0.00018153589812667096</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -1894,7 +1894,7 @@
         <v>3366.0</v>
       </c>
       <c r="B189">
-        <v>6.980664538455042e-60</v>
+        <v>0.0001820539898760669</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -1902,7 +1902,7 @@
         <v>3384.0</v>
       </c>
       <c r="B190">
-        <v>7.449474426078027e-60</v>
+        <v>0.00018256511605579639</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -1910,7 +1910,7 @@
         <v>3402.0</v>
       </c>
       <c r="B191">
-        <v>7.946995189395681e-60</v>
+        <v>0.00018306922501022592</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -1918,7 +1918,7 @@
         <v>3420.0</v>
       </c>
       <c r="B192">
-        <v>8.47481717079433e-60</v>
+        <v>0.00018356626508372203</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -1926,7 +1926,7 @@
         <v>3438.0</v>
       </c>
       <c r="B193">
-        <v>9.034609313247571e-60</v>
+        <v>0.00018405618462065122</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -1934,7 +1934,7 @@
         <v>3456.0</v>
       </c>
       <c r="B194">
-        <v>9.628123201626698e-60</v>
+        <v>0.00018453949684900503</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -1942,7 +1942,7 @@
         <v>3474.0</v>
       </c>
       <c r="B195">
-        <v>1.025719609387969e-59</v>
+        <v>0.00018501723285329906</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -1950,7 +1950,7 @@
         <v>3492.0</v>
       </c>
       <c r="B196">
-        <v>1.0923754961286861e-59</v>
+        <v>0.000185489327940968</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -1958,7 +1958,7 @@
         <v>3510.0</v>
       </c>
       <c r="B197">
-        <v>1.162982040903355e-59</v>
+        <v>0.00018595568816680204</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -1966,7 +1966,7 @@
         <v>3528.0</v>
       </c>
       <c r="B198">
-        <v>1.2377510282042069e-59</v>
+        <v>0.00018641621958559137</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -1974,7 +1974,7 @@
         <v>3546.0</v>
       </c>
       <c r="B199">
-        <v>1.3169044497776638e-59</v>
+        <v>0.00018687082825212612</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -1982,7 +1982,7 @@
         <v>3564.0</v>
       </c>
       <c r="B200">
-        <v>1.400674865046341e-59</v>
+        <v>0.00018731942022119652</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -1990,7 +1990,7 @@
         <v>3582.0</v>
       </c>
       <c r="B201">
-        <v>1.489305897021168e-59</v>
+        <v>0.00018776190154759279</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -1998,7 +1998,7 @@
         <v>3600.0</v>
       </c>
       <c r="B202">
-        <v>1.5830526843024996e-59</v>
+        <v>0.00018819817828610503</v>
       </c>
     </row>
   </sheetData>
